--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1306,90 @@
         <v>46002.79906769676</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>270</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>608042333</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>46002.82018770833</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46018</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>270</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Juan Grau</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>juan@mail.com</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>608093242</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>46006.65202089283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1381,13 +1381,95 @@
           <t>juan@mail.com</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>608093242</t>
-        </is>
+      <c r="J24" t="n">
+        <v>608093242</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>46006.65202089283</v>
+        <v>46006.6520208912</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>500</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>609298323</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>46008.75141721065</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>780</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>yolanda reig</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>yolanda.reig1@gmail.com</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6492627281</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>46016.52134538213</v>
       </c>
     </row>
   </sheetData>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,6 +488,26 @@
           <t>created_at</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cliente_dni</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>precio_noche_final</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>precio_noche_base</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>descuento_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -527,6 +547,10 @@
       <c r="K2" s="2" t="n">
         <v>45828.42708333334</v>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -566,6 +590,10 @@
       <c r="K3" s="2" t="n">
         <v>45828.43055555555</v>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -597,6 +625,10 @@
       <c r="K4" s="2" t="n">
         <v>45980.68328703703</v>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -628,6 +660,10 @@
       <c r="K5" s="2" t="n">
         <v>45980.68871811342</v>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -659,6 +695,10 @@
       <c r="K6" s="2" t="n">
         <v>45980.68957274305</v>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -690,6 +730,10 @@
       <c r="K7" s="2" t="n">
         <v>45980.69020590278</v>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -731,6 +775,10 @@
       <c r="K8" s="2" t="n">
         <v>45980.69679616898</v>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -772,6 +820,10 @@
       <c r="K9" s="2" t="n">
         <v>45980.70625211806</v>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -813,6 +865,10 @@
       <c r="K10" s="2" t="n">
         <v>45980.71811115741</v>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -854,6 +910,10 @@
       <c r="K11" s="2" t="n">
         <v>45980.72272252315</v>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -895,6 +955,10 @@
       <c r="K12" s="2" t="n">
         <v>45980.72667157408</v>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -936,6 +1000,10 @@
       <c r="K13" s="2" t="n">
         <v>45981.66200387732</v>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -977,6 +1045,10 @@
       <c r="K14" s="2" t="n">
         <v>45981.72657297453</v>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1018,6 +1090,10 @@
       <c r="K15" s="2" t="n">
         <v>45981.7974350463</v>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1059,6 +1135,10 @@
       <c r="K16" s="2" t="n">
         <v>45982.81956030092</v>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1100,6 +1180,10 @@
       <c r="K17" s="2" t="n">
         <v>45994.64569677084</v>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1141,6 +1225,10 @@
       <c r="K18" s="2" t="n">
         <v>45994.68240884259</v>
       </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1182,6 +1270,10 @@
       <c r="K19" s="2" t="n">
         <v>45994.68277976852</v>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1223,6 +1315,10 @@
       <c r="K20" s="2" t="n">
         <v>45994.68714504629</v>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1264,6 +1360,10 @@
       <c r="K21" s="2" t="n">
         <v>46002.55284238426</v>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1305,6 +1405,10 @@
       <c r="K22" s="2" t="n">
         <v>46002.79906769676</v>
       </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1346,6 +1450,10 @@
       <c r="K23" s="2" t="n">
         <v>46002.82018770833</v>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1387,6 +1495,10 @@
       <c r="K24" s="2" t="n">
         <v>46006.6520208912</v>
       </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1428,6 +1540,10 @@
       <c r="K25" s="2" t="n">
         <v>46008.75141721065</v>
       </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1463,13 +1579,223 @@
           <t>yolanda.reig1@gmail.com</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>6492627281</t>
-        </is>
+      <c r="J26" t="n">
+        <v>6492627281</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>46016.52134538213</v>
+        <v>46016.52134538195</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>375</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>cancelada</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Juan Grau</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>juan.grau@gmail.com</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>46034.57130006944</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20909090M</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>375</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Juan Grau</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>juan.grau@gmail.com</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>609090909</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>46034.58982851852</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>20090909M</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>laura@mail.com</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>600123456</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>46034.66179443287</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>12345678Z</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>125</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>260</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ana@x.com</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>699888777</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>46034.66325032408</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>11223344B</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>130</v>
+      </c>
+      <c r="N30" t="n">
+        <v>130</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,283 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>420</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Juan Grau</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>609090909</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>46034.82148997685</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>20933939H</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>140</v>
+      </c>
+      <c r="N31" t="n">
+        <v>140</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>280</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>609080808</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>46034.82740875</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>20202020M</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>140</v>
+      </c>
+      <c r="N32" t="n">
+        <v>140</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>560</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>cancelada</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>609090909</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>46034.86144533565</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>20202020M</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>140</v>
+      </c>
+      <c r="N33" t="n">
+        <v>140</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>560</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>606060606</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>46034.87013637731</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>20202020M</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>140</v>
+      </c>
+      <c r="N34" t="n">
+        <v>140</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>280</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>609090909</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46034.90321970693</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>20909090M</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>140</v>
+      </c>
+      <c r="N35" t="n">
+        <v>140</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,7 +547,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>45828.42708333334</v>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -587,7 +590,7 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>45828.43055555555</v>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -619,10 +622,18 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>45980.68328703703</v>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -654,10 +665,18 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>45980.68871811342</v>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -689,10 +708,18 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>45980.68957274305</v>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -724,10 +751,18 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>45980.69020590278</v>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -772,7 +807,7 @@
       <c r="J8" t="n">
         <v>34600123456</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>45980.69679616898</v>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -817,7 +852,7 @@
       <c r="J9" t="n">
         <v>600123456</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>45980.70625211806</v>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -862,7 +897,7 @@
       <c r="J10" t="n">
         <v>600123456</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>45980.71811115741</v>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -907,7 +942,7 @@
       <c r="J11" t="n">
         <v>600123456</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>45980.72272252315</v>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -952,7 +987,7 @@
       <c r="J12" t="n">
         <v>600123456</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>45980.72667157408</v>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -997,7 +1032,7 @@
       <c r="J13" t="n">
         <v>608049237</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>45981.66200387732</v>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1042,7 +1077,7 @@
       <c r="J14" t="n">
         <v>608023113</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>45981.72657297453</v>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1087,7 +1122,7 @@
       <c r="J15" t="n">
         <v>688888888</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>45981.7974350463</v>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1132,7 +1167,7 @@
       <c r="J16" t="n">
         <v>600123456</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>45982.81956030092</v>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1177,7 +1212,7 @@
       <c r="J17" t="n">
         <v>600123456</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>45994.64569677084</v>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1222,7 +1257,7 @@
       <c r="J18" t="n">
         <v>600123456</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>45994.68240884259</v>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1267,7 +1302,7 @@
       <c r="J19" t="n">
         <v>600987654</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>45994.68277976852</v>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1312,7 +1347,7 @@
       <c r="J20" t="n">
         <v>608049237</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>45994.68714504629</v>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1357,7 +1392,7 @@
       <c r="J21" t="n">
         <v>6080492367</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>46002.55284238426</v>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1402,7 +1437,7 @@
       <c r="J22" t="n">
         <v>608080808</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>46002.79906769676</v>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1447,7 +1482,7 @@
       <c r="J23" t="n">
         <v>608042333</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>46002.82018770833</v>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1492,7 +1527,7 @@
       <c r="J24" t="n">
         <v>608093242</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>46006.6520208912</v>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1514,7 +1549,7 @@
         <v>46034</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>500</v>
@@ -1537,7 +1572,7 @@
       <c r="J25" t="n">
         <v>609298323</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>46008.75141721065</v>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1566,7 +1601,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>creada</t>
+          <t>cancelada</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1582,7 +1617,7 @@
       <c r="J26" t="n">
         <v>6492627281</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>46016.52134538195</v>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1627,7 +1662,7 @@
       <c r="J27" t="n">
         <v>600000000</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>46034.57130006944</v>
       </c>
       <c r="L27" t="inlineStr">
@@ -1676,7 +1711,7 @@
       <c r="J28" t="n">
         <v>609090909</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>46034.58982851852</v>
       </c>
       <c r="L28" t="inlineStr">
@@ -1725,7 +1760,7 @@
       <c r="J29" t="n">
         <v>600123456</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>46034.66179443287</v>
       </c>
       <c r="L29" t="inlineStr">
@@ -1780,7 +1815,7 @@
       <c r="J30" t="n">
         <v>699888777</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>46034.66325032408</v>
       </c>
       <c r="L30" t="inlineStr">
@@ -1835,7 +1870,7 @@
       <c r="J31" t="n">
         <v>609090909</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>46034.82148997685</v>
       </c>
       <c r="L31" t="inlineStr">
@@ -1890,7 +1925,7 @@
       <c r="J32" t="n">
         <v>609080808</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>46034.82740875</v>
       </c>
       <c r="L32" t="inlineStr">
@@ -1945,7 +1980,7 @@
       <c r="J33" t="n">
         <v>609090909</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>46034.86144533565</v>
       </c>
       <c r="L33" t="inlineStr">
@@ -2000,7 +2035,7 @@
       <c r="J34" t="n">
         <v>606060606</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>46034.87013637731</v>
       </c>
       <c r="L34" t="inlineStr">
@@ -2052,13 +2087,11 @@
           <t>juan@gmail.com</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>609090909</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>46034.90321970693</v>
+      <c r="J35" t="n">
+        <v>609090909</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>46034.90321971065</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>creada</t>
+          <t>cancelada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1099,7 +1099,7 @@
         <v>45852</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>210</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>creada</t>
+          <t>cancelada</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2108,6 +2108,116 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46392</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46397</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>700</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Juan Grau</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>606060606</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>46035.7954537037</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>20202020M</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>140</v>
+      </c>
+      <c r="N36" t="n">
+        <v>140</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>354.9</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>cancelada</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Juan Grau</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>609090909</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46035.79765993055</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>20909090M</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>130</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +544,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>45828.42708333334</v>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -576,7 +573,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>creada</t>
+          <t>cancelada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -590,7 +587,7 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>45828.43055555555</v>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -622,18 +619,10 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>45980.68328703703</v>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -665,18 +654,10 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>45980.68871811342</v>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -708,18 +689,10 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>45980.68957274305</v>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -751,18 +724,10 @@
           <t>creada</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>45980.69020590278</v>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -807,7 +772,7 @@
       <c r="J8" t="n">
         <v>34600123456</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>45980.69679616898</v>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -852,7 +817,7 @@
       <c r="J9" t="n">
         <v>600123456</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>45980.70625211806</v>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -897,7 +862,7 @@
       <c r="J10" t="n">
         <v>600123456</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>45980.71811115741</v>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -942,7 +907,7 @@
       <c r="J11" t="n">
         <v>600123456</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>45980.72272252315</v>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -987,7 +952,7 @@
       <c r="J12" t="n">
         <v>600123456</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>45980.72667157408</v>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1032,7 +997,7 @@
       <c r="J13" t="n">
         <v>608049237</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>45981.66200387732</v>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1077,7 +1042,7 @@
       <c r="J14" t="n">
         <v>608023113</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>45981.72657297453</v>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1122,7 +1087,7 @@
       <c r="J15" t="n">
         <v>688888888</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>45981.7974350463</v>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1167,7 +1132,7 @@
       <c r="J16" t="n">
         <v>600123456</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>45982.81956030092</v>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1212,7 +1177,7 @@
       <c r="J17" t="n">
         <v>600123456</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>45994.64569677084</v>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1257,7 +1222,7 @@
       <c r="J18" t="n">
         <v>600123456</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>45994.68240884259</v>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1302,7 +1267,7 @@
       <c r="J19" t="n">
         <v>600987654</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>45994.68277976852</v>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1347,7 +1312,7 @@
       <c r="J20" t="n">
         <v>608049237</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>45994.68714504629</v>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1392,7 +1357,7 @@
       <c r="J21" t="n">
         <v>6080492367</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>46002.55284238426</v>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1437,7 +1402,7 @@
       <c r="J22" t="n">
         <v>608080808</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>46002.79906769676</v>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1482,7 +1447,7 @@
       <c r="J23" t="n">
         <v>608042333</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>46002.82018770833</v>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1527,7 +1492,7 @@
       <c r="J24" t="n">
         <v>608093242</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>46006.6520208912</v>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1572,7 +1537,7 @@
       <c r="J25" t="n">
         <v>609298323</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>46008.75141721065</v>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1617,7 +1582,7 @@
       <c r="J26" t="n">
         <v>6492627281</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>46016.52134538195</v>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1662,7 +1627,7 @@
       <c r="J27" t="n">
         <v>600000000</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>46034.57130006944</v>
       </c>
       <c r="L27" t="inlineStr">
@@ -1711,7 +1676,7 @@
       <c r="J28" t="n">
         <v>609090909</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>46034.58982851852</v>
       </c>
       <c r="L28" t="inlineStr">
@@ -1760,7 +1725,7 @@
       <c r="J29" t="n">
         <v>600123456</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>46034.66179443287</v>
       </c>
       <c r="L29" t="inlineStr">
@@ -1815,7 +1780,7 @@
       <c r="J30" t="n">
         <v>699888777</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>46034.66325032408</v>
       </c>
       <c r="L30" t="inlineStr">
@@ -1870,7 +1835,7 @@
       <c r="J31" t="n">
         <v>609090909</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>46034.82148997685</v>
       </c>
       <c r="L31" t="inlineStr">
@@ -1925,7 +1890,7 @@
       <c r="J32" t="n">
         <v>609080808</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>46034.82740875</v>
       </c>
       <c r="L32" t="inlineStr">
@@ -1980,7 +1945,7 @@
       <c r="J33" t="n">
         <v>609090909</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>46034.86144533565</v>
       </c>
       <c r="L33" t="inlineStr">
@@ -2035,7 +2000,7 @@
       <c r="J34" t="n">
         <v>606060606</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>46034.87013637731</v>
       </c>
       <c r="L34" t="inlineStr">
@@ -2090,7 +2055,7 @@
       <c r="J35" t="n">
         <v>609090909</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>46034.90321971065</v>
       </c>
       <c r="L35" t="inlineStr">
@@ -2145,7 +2110,7 @@
       <c r="J36" t="n">
         <v>606060606</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>46035.7954537037</v>
       </c>
       <c r="L36" t="inlineStr">
@@ -2200,7 +2165,7 @@
       <c r="J37" t="n">
         <v>609090909</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>46035.79765993055</v>
       </c>
       <c r="L37" t="inlineStr">
@@ -2216,6 +2181,118 @@
       </c>
       <c r="O37" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Gemma Alpuente y Elena Alpuente</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>hola@gmail.com</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>676676676</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>46072.71301862269</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>45678945J</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>140</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>creada</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>juan</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>juan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>609090909</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>46072.76322210649</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>20202020M</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>125</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>

--- a/data/reservas.xlsx
+++ b/data/reservas.xlsx
@@ -2246,16 +2246,16 @@
         <v>1</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>46079</v>
+        <v>46106</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>307.5</v>
+        <v>250</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2272,10 +2272,8 @@
           <t>juan@gmail.com</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>609090909</t>
-        </is>
+      <c r="J39" t="n">
+        <v>609090909</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>46072.76322210649</v>
@@ -2286,13 +2284,13 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>102.5</v>
+        <v>125</v>
       </c>
       <c r="N39" t="n">
         <v>125</v>
       </c>
       <c r="O39" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
